--- a/subscription_forms/006_cultural_program_subscription_form--subscription_forms.xlsx
+++ b/subscription_forms/006_cultural_program_subscription_form--subscription_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -714,144 +714,6 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -872,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -918,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -935,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -952,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -969,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -986,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
